--- a/doctool/test/auto/scenario23/システム機能設計書_サンプル_S23.xlsx
+++ b/doctool/test/auto/scenario23/システム機能設計書_サンプル_S23.xlsx
@@ -2266,6 +2266,12 @@
 ※レビュー日時を書く場合はコロンの直後に*を書く。</t>
       </text>
     </comment>
+    <comment ref="D50" authorId="1" shapeId="0">
+      <text>
+        <t>山田　太郎:z
+未登録カテゴリの指摘コメントの例。</t>
+      </text>
+    </comment>
     <comment ref="E60" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:b
@@ -2282,24 +2288,6 @@
 最後の行に「済」と書くと指摘をクローズできる。
 「済」の前にスペースを空けて確認日と確認者を書くこともできる。
 08/02山田 済</t>
-      </text>
-    </comment>
-    <comment ref="E63" authorId="1" shapeId="0">
-      <text>
-        <t>山田　太郎:d
-機能・仕様誤りの指摘例（カテゴリd）。</t>
-      </text>
-    </comment>
-    <comment ref="E64" authorId="1" shapeId="0">
-      <text>
-        <t>山田　太郎:e
-設計・ドキュメント規約違反の指摘例（カテゴリe）。</t>
-      </text>
-    </comment>
-    <comment ref="E65" authorId="1" shapeId="0">
-      <text>
-        <t>山田　太郎:f
-記述誤りの指摘例（カテゴリf）。</t>
       </text>
     </comment>
     <comment ref="A71" authorId="0" shapeId="0">

--- a/doctool/test/auto/scenario23/システム機能設計書_サンプル_S23.xlsx
+++ b/doctool/test/auto/scenario23/システム機能設計書_サンプル_S23.xlsx
@@ -2246,7 +2246,6 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>作成者</author>
-    <author>山田　太郎</author>
   </authors>
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
@@ -2264,12 +2263,6 @@
 レビュー指摘コメントの例。
 自動で挿入される名前とコロンの直後に指摘分類をa～iで書く。
 ※レビュー日時を書く場合はコロンの直後に*を書く。</t>
-      </text>
-    </comment>
-    <comment ref="D50" authorId="1" shapeId="0">
-      <text>
-        <t>山田　太郎:z
-未登録カテゴリの指摘コメントの例。</t>
       </text>
     </comment>
     <comment ref="E60" authorId="0" shapeId="0">
@@ -3361,7 +3354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN33"/>
+  <dimension ref="A1:AN34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="4.83203125" defaultRowHeight="11.25"/>
   <sheetData>
     <row r="1" customFormat="1" s="11">
@@ -16598,6 +16591,7 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="E65" t="inlineStr">
         <is>
@@ -16605,6 +16599,7 @@
         </is>
       </c>
     </row>
+    <row r="66"/>
     <row r="70">
       <c r="A70" s="94" t="n"/>
     </row>
